--- a/ValueSet-MITRE-ATTCK-Parent-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Parent-Techniques.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.8</t>
+    <t>0.0.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T10:01:26+00:00</t>
+    <t>2026-05-14T18:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
